--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_237_R24.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_237_R24.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.5138</v>
+        <v>5.9417</v>
       </c>
       <c r="E2" t="n">
-        <v>2.8914</v>
+        <v>3.084</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6224</v>
+        <v>2.8577</v>
       </c>
       <c r="G2" t="n">
         <v>2.9139</v>
@@ -610,13 +610,13 @@
         <v>1.1598</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7042</v>
+        <v>-0.2763</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5228</v>
+        <v>-0.3301</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1814</v>
+        <v>0.0538</v>
       </c>
       <c r="V2" t="n">
         <v>2.1444</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.9222</v>
+        <v>4.3995</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7028</v>
+        <v>0.8522</v>
       </c>
       <c r="F3" t="n">
-        <v>4.2194</v>
+        <v>3.5473</v>
       </c>
       <c r="G3" t="n">
         <v>2.9054</v>
@@ -688,13 +688,13 @@
         <v>2.3195</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5683</v>
+        <v>1.0455</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0351</v>
+        <v>0.1142</v>
       </c>
       <c r="U3" t="n">
-        <v>1.6035</v>
+        <v>0.9313</v>
       </c>
       <c r="V3" t="n">
         <v>1.6083</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3887</v>
+        <v>3.2192</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6816</v>
+        <v>0.9489</v>
       </c>
       <c r="F4" t="n">
-        <v>2.7071</v>
+        <v>2.2702</v>
       </c>
       <c r="G4" t="n">
         <v>3.3465</v>
@@ -766,13 +766,13 @@
         <v>1.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0479</v>
+        <v>-0.2174</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5975</v>
+        <v>-0.3301</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5496</v>
+        <v>0.1127</v>
       </c>
       <c r="V4" t="n">
         <v>-0.1418</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5238</v>
+        <v>3.1876</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5416</v>
+        <v>0.9701</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9822</v>
+        <v>2.2174</v>
       </c>
       <c r="G5" t="n">
         <v>2.179</v>
@@ -844,13 +844,13 @@
         <v>0.6959</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7121</v>
+        <v>-0.0483</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5228</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1893</v>
+        <v>0.0459</v>
       </c>
       <c r="V5" t="n">
         <v>2.6805</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9839</v>
+        <v>2.7223</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9889</v>
+        <v>-0.4857</v>
       </c>
       <c r="F6" t="n">
-        <v>2.9728</v>
+        <v>3.208</v>
       </c>
       <c r="G6" t="n">
         <v>3.7116</v>
@@ -922,13 +922,13 @@
         <v>2.0876</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2665</v>
+        <v>-0.528</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8215</v>
+        <v>-0.3183</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.445</v>
+        <v>-0.2098</v>
       </c>
       <c r="V6" t="n">
         <v>0.9304</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1423</v>
+        <v>1.7149</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.598</v>
+        <v>-0.1262</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7403</v>
+        <v>1.8411</v>
       </c>
       <c r="G7" t="n">
         <v>1.9621</v>
@@ -1000,13 +1000,13 @@
         <v>1.3917</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.4229</v>
+        <v>-0.8502999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8962</v>
+        <v>-0.4244</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5266999999999999</v>
+        <v>-0.4259</v>
       </c>
       <c r="V7" t="n">
         <v>-0.7886</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. BIRCH</t>
+          <t>M. MAHMUTOGLU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2965</v>
+        <v>0.0221</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1576</v>
+        <v>0.1399</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4541</v>
+        <v>-0.1178</v>
       </c>
       <c r="G8" t="n">
-        <v>0.913</v>
+        <v>-0.2198</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0698</v>
+        <v>-0.1896</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8431999999999999</v>
+        <v>-0.0301</v>
       </c>
       <c r="J8" t="n">
-        <v>0.749</v>
+        <v>0.3914</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6385999999999999</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1104</v>
+        <v>0.3914</v>
       </c>
       <c r="M8" t="n">
-        <v>0.164</v>
+        <v>-0.6112</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5688</v>
+        <v>-0.1896</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7328</v>
+        <v>-0.4216</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.3917</v>
+        <v>0.4639</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.3195</v>
+        <v>-0.232</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3809</v>
+        <v>-0.2221</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4129</v>
+        <v>-0.0196</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0321</v>
+        <v>-0.2025</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3943</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3943</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. MAHMUTOGLU</t>
+          <t>K. BIRCH</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.399</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2139</v>
+        <v>-1.3621</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1851</v>
+        <v>1.3532</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2198</v>
+        <v>0.913</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1896</v>
+        <v>0.0698</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0301</v>
+        <v>0.8431999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3914</v>
+        <v>0.749</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>0.6385999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3914</v>
+        <v>0.1104</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6112</v>
+        <v>0.164</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1896</v>
+        <v>-0.5688</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4216</v>
+        <v>0.7328</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4639</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.232</v>
+        <v>-2.3195</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6431</v>
+        <v>0.0756</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3734</v>
+        <v>0.2084</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2697</v>
+        <v>-0.1329</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.3943</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6142</v>
+        <v>-0.8336</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7635999999999999</v>
+        <v>-1.1174</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1494</v>
+        <v>0.2838</v>
       </c>
       <c r="G10" t="n">
         <v>0.0667</v>
@@ -1234,13 +1234,13 @@
         <v>1.1598</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7108</v>
+        <v>0.4914</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4876</v>
+        <v>0.1338</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2232</v>
+        <v>0.3576</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. BACOT JR.</t>
+          <t>M. JANTUNEN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7727</v>
+        <v>-1.8918</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1794</v>
+        <v>-2.4547</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.5933</v>
+        <v>0.5629</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.9687</v>
+        <v>-0.1006</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.1729</v>
+        <v>1.0337</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2041</v>
+        <v>-1.1343</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.1116</v>
+        <v>-0.8941</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.9509</v>
+        <v>0.605</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.1607</v>
+        <v>-1.4991</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1428</v>
+        <v>0.7935</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.222</v>
+        <v>0.4287</v>
       </c>
       <c r="O11" t="n">
         <v>0.3648</v>
       </c>
       <c r="P11" t="n">
-        <v>0.232</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>-1.3917</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6237</v>
+        <v>1.3917</v>
       </c>
       <c r="S11" t="n">
-        <v>2.1807</v>
+        <v>0.6368</v>
       </c>
       <c r="T11" t="n">
-        <v>2.3239</v>
+        <v>-0.1689</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1432</v>
+        <v>0.8057</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.2166</v>
+        <v>-2.428</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.2166</v>
+        <v>-2.428</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. JANTUNEN</t>
+          <t>A. BACOT JR.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.1113</v>
+        <v>-3.2731</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8086</v>
+        <v>-1.9487</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6973</v>
+        <v>-1.3245</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1006</v>
+        <v>-0.9687</v>
       </c>
       <c r="H12" t="n">
-        <v>1.0337</v>
+        <v>-1.1729</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.1343</v>
+        <v>0.2041</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.8941</v>
+        <v>-1.1116</v>
       </c>
       <c r="K12" t="n">
-        <v>0.605</v>
+        <v>-0.9509</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.4991</v>
+        <v>-0.1607</v>
       </c>
       <c r="M12" t="n">
-        <v>0.7935</v>
+        <v>0.1428</v>
       </c>
       <c r="N12" t="n">
-        <v>0.4287</v>
+        <v>-0.222</v>
       </c>
       <c r="O12" t="n">
         <v>0.3648</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>0.232</v>
       </c>
       <c r="Q12" t="n">
         <v>-1.3917</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4173</v>
+        <v>0.6803</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5228</v>
+        <v>0.5546</v>
       </c>
       <c r="U12" t="n">
-        <v>0.9401</v>
+        <v>0.1256</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.428</v>
+        <v>-3.2166</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.428</v>
+        <v>-3.2166</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.746</v>
+        <v>-3.3249</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.6638</v>
+        <v>-2.31</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.0821</v>
+        <v>-1.0149</v>
       </c>
       <c r="G13" t="n">
         <v>0.9283</v>
@@ -1468,13 +1468,13 @@
         <v>1.3917</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6589</v>
+        <v>-0.2379</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5228</v>
+        <v>-0.1689</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1362</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-0.5361</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>11.128</v>
+        <v>11.8751</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.556400000000001</v>
+        <v>-3.8097</v>
       </c>
       <c r="F14" t="n">
-        <v>15.6845</v>
+        <v>15.6844</v>
       </c>
       <c r="G14" t="n">
         <v>17.6374</v>
@@ -1522,7 +1522,7 @@
         <v>10.2955</v>
       </c>
       <c r="K14" t="n">
-        <v>5.7961</v>
+        <v>5.796100000000001</v>
       </c>
       <c r="L14" t="n">
         <v>4.4993</v>
@@ -1546,13 +1546,13 @@
         <v>16.2368</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1976000000000004</v>
+        <v>0.5493000000000002</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.5905</v>
+        <v>-0.8435000000000004</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3928</v>
+        <v>1.3925</v>
       </c>
       <c r="V14" t="n">
         <v>0.6467999999999996</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.7724</v>
+        <v>5.1383</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9828</v>
+        <v>1.4494</v>
       </c>
       <c r="F15" t="n">
-        <v>3.7896</v>
+        <v>3.6888</v>
       </c>
       <c r="G15" t="n">
         <v>0.8642</v>
@@ -1624,13 +1624,13 @@
         <v>3.7112</v>
       </c>
       <c r="S15" t="n">
-        <v>2.233</v>
+        <v>0.5988</v>
       </c>
       <c r="T15" t="n">
-        <v>2.1077</v>
+        <v>0.5744</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1252</v>
+        <v>0.0244</v>
       </c>
       <c r="V15" t="n">
         <v>1.3558</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.9363</v>
+        <v>1.1835</v>
       </c>
       <c r="E16" t="n">
-        <v>3.0911</v>
+        <v>1.2039</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1547</v>
+        <v>-0.0203</v>
       </c>
       <c r="G16" t="n">
         <v>0.1652</v>
@@ -1702,13 +1702,13 @@
         <v>1.6237</v>
       </c>
       <c r="S16" t="n">
-        <v>2.5391</v>
+        <v>0.7863</v>
       </c>
       <c r="T16" t="n">
-        <v>2.4732</v>
+        <v>0.586</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0659</v>
+        <v>0.2003</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7063</v>
+        <v>0.9258</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7433</v>
+        <v>1.0971</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.037</v>
+        <v>-0.1714</v>
       </c>
       <c r="G17" t="n">
         <v>0.3479</v>
@@ -1780,13 +1780,13 @@
         <v>0.4639</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1054</v>
+        <v>0.114</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4481</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3427</v>
+        <v>0.2082</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4644</v>
+        <v>0.7174</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2912</v>
+        <v>0.0626</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7556</v>
+        <v>0.6548</v>
       </c>
       <c r="G18" t="n">
         <v>-0.7696</v>
@@ -1858,13 +1858,13 @@
         <v>1.3917</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0742</v>
+        <v>0.3273</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5228</v>
+        <v>-0.1689</v>
       </c>
       <c r="U18" t="n">
-        <v>0.597</v>
+        <v>0.4962</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. JOKSIMOVIC</t>
+          <t>K. SIMMONS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1124</v>
+        <v>0.4153</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0536</v>
+        <v>-0.1852</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.166</v>
+        <v>0.6004</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1572</v>
+        <v>0.2847</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1741</v>
+        <v>2.821</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3312</v>
+        <v>-2.5363</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0536</v>
+        <v>0.9211</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0168</v>
+        <v>3.2434</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0368</v>
+        <v>-2.3222</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2108</v>
+        <v>-0.6364</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1573</v>
+        <v>-0.4223</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.368</v>
+        <v>-0.214</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.9278</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.5515</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>3.4793</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0448</v>
+        <v>-1.4752</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>-0.841</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0448</v>
+        <v>-0.6341</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.2862</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>K. SIMMONS</t>
+          <t>S. JOKSIMOVIC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1739</v>
+        <v>0.1908</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.539</v>
+        <v>0.2895</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3652</v>
+        <v>-0.0988</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2847</v>
+        <v>-0.1572</v>
       </c>
       <c r="H20" t="n">
-        <v>2.821</v>
+        <v>0.1741</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.5363</v>
+        <v>-0.3312</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9211</v>
+        <v>0.0536</v>
       </c>
       <c r="K20" t="n">
-        <v>3.2434</v>
+        <v>0.0168</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.3222</v>
+        <v>0.0368</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6364</v>
+        <v>-0.2108</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4223</v>
+        <v>0.1573</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.214</v>
+        <v>-0.368</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9278</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.5515</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>3.4793</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.0643</v>
+        <v>0.3479</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.1949</v>
+        <v>0.2359</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8694</v>
+        <v>0.112</v>
       </c>
       <c r="V20" t="n">
-        <v>0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.2862</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. DIAKITE</t>
+          <t>T. FORREST</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0811</v>
+        <v>-1.2276</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.4247</v>
+        <v>-2.8737</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3436</v>
+        <v>1.6461</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.08550000000000001</v>
+        <v>-3.7846</v>
       </c>
       <c r="H21" t="n">
-        <v>1.1224</v>
+        <v>-3.4634</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.2079</v>
+        <v>-0.3212</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8942</v>
+        <v>-2.6976</v>
       </c>
       <c r="K21" t="n">
-        <v>1.6805</v>
+        <v>-2.5369</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.7863</v>
+        <v>-0.1607</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.9796</v>
+        <v>-1.087</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5581</v>
+        <v>-0.9265</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4216</v>
+        <v>-0.1605</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.5515</v>
+        <v>-1.3917</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3917</v>
+        <v>2.3195</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5834</v>
+        <v>0.0209</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5149</v>
+        <v>-0.3927</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.4136</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2525</v>
+        <v>1.6083</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.2525</v>
+        <v>1.6083</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. SPAGNOLO</t>
+          <t>M. DIAKITE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.1141</v>
+        <v>-1.6765</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8845</v>
+        <v>-1.9529</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2296</v>
+        <v>0.2763</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.0136</v>
+        <v>-0.08550000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4873</v>
+        <v>1.1224</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.5262</v>
+        <v>-1.2079</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.5402</v>
+        <v>0.8942</v>
       </c>
       <c r="K22" t="n">
-        <v>0.4068</v>
+        <v>1.6805</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.947</v>
+        <v>-0.7863</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.4734</v>
+        <v>-0.9796</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8942</v>
+        <v>-0.5581</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.5792</v>
+        <v>-0.4216</v>
       </c>
       <c r="P22" t="n">
-        <v>0.6959</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.3917</v>
+        <v>-2.5515</v>
       </c>
       <c r="R22" t="n">
-        <v>2.0876</v>
+        <v>1.3917</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4872</v>
+        <v>-0.1788</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0474</v>
+        <v>-0.0431</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4397</v>
+        <v>-0.1357</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.2836</v>
+        <v>-0.2525</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.2525</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2836</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>T. FORREST</t>
+          <t>M. SPAGNOLO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.3393</v>
+        <v>-1.979</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.8173</v>
+        <v>-1.6486</v>
       </c>
       <c r="F23" t="n">
-        <v>1.478</v>
+        <v>-0.3305</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.7846</v>
+        <v>-3.0136</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.4634</v>
+        <v>-0.4873</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3212</v>
+        <v>-2.5262</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.6976</v>
+        <v>-0.5402</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.5369</v>
+        <v>0.4068</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.1607</v>
+        <v>-0.947</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.087</v>
+        <v>-2.4734</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.9265</v>
+        <v>-0.8942</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.1605</v>
+        <v>-1.5792</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="Q23" t="n">
         <v>-1.3917</v>
       </c>
       <c r="R23" t="n">
-        <v>2.3195</v>
+        <v>2.0876</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0908</v>
+        <v>0.6223</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.3364</v>
+        <v>0.2833</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2456</v>
+        <v>0.3389</v>
       </c>
       <c r="V23" t="n">
-        <v>1.6083</v>
+        <v>-0.2836</v>
       </c>
       <c r="W23" t="n">
-        <v>1.6083</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.0377</v>
+        <v>-2.9204</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.9473</v>
+        <v>-2.0652</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0904</v>
+        <v>-0.8552</v>
       </c>
       <c r="G24" t="n">
         <v>-3.015</v>
@@ -2326,13 +2326,13 @@
         <v>1.8556</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5742</v>
+        <v>-0.4569</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3339</v>
+        <v>-0.4518</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2403</v>
+        <v>-0.005</v>
       </c>
       <c r="V24" t="n">
         <v>-1.0722</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.5054</v>
+        <v>-5.3361</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.539</v>
+        <v>-5.0672</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0336</v>
+        <v>-0.2689</v>
       </c>
       <c r="G25" t="n">
         <v>-4.0639</v>
@@ -2404,13 +2404,13 @@
         <v>2.0876</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4415</v>
+        <v>-0.2721</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.4936</v>
+        <v>-1.0218</v>
       </c>
       <c r="U25" t="n">
-        <v>1.0521</v>
+        <v>0.7497</v>
       </c>
       <c r="V25" t="n">
         <v>-0.5361</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.6437</v>
+        <v>-6.5594</v>
       </c>
       <c r="E26" t="n">
-        <v>-6.1122</v>
+        <v>-5.9942</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.5315</v>
+        <v>-0.5651</v>
       </c>
       <c r="G26" t="n">
         <v>-4.4101</v>
@@ -2482,13 +2482,13 @@
         <v>2.7834</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.3211</v>
+        <v>-0.2368</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.1766</v>
+        <v>-0.0587</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.1445</v>
+        <v>-0.1781</v>
       </c>
       <c r="V26" t="n">
         <v>-2.1444</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-11.1282</v>
+        <v>-11.1279</v>
       </c>
       <c r="E27" t="n">
-        <v>-15.6844</v>
+        <v>-15.6845</v>
       </c>
       <c r="F27" t="n">
-        <v>4.5564</v>
+        <v>4.556199999999999</v>
       </c>
       <c r="G27" t="n">
         <v>-17.6375</v>
@@ -2539,7 +2539,7 @@
         <v>-0.5485000000000004</v>
       </c>
       <c r="L27" t="n">
-        <v>-6.793099999999999</v>
+        <v>-6.7931</v>
       </c>
       <c r="M27" t="n">
         <v>-10.2956</v>
@@ -2560,22 +2560,22 @@
         <v>23.1952</v>
       </c>
       <c r="S27" t="n">
-        <v>0.1975999999999999</v>
+        <v>0.1977</v>
       </c>
       <c r="T27" t="n">
-        <v>-1.392900000000001</v>
+        <v>-1.3926</v>
       </c>
       <c r="U27" t="n">
-        <v>1.5903</v>
+        <v>1.5904</v>
       </c>
       <c r="V27" t="n">
         <v>-0.6468</v>
       </c>
       <c r="W27" t="n">
-        <v>9.2866</v>
+        <v>9.286600000000002</v>
       </c>
       <c r="X27" t="n">
-        <v>-9.933400000000001</v>
+        <v>-9.933399999999999</v>
       </c>
     </row>
   </sheetData>
